--- a/data/trans_camb/PCS12_SP_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 8,04</t>
+          <t>-0,02; 8,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 8,44</t>
+          <t>-0,63; 8,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 17,92</t>
+          <t>8,12; 17,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 7,13</t>
+          <t>-0,69; 7,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 6,45</t>
+          <t>-2,21; 6,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 15,87</t>
+          <t>8,01; 15,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,87</t>
+          <t>1,16; 7,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 5,99</t>
+          <t>-0,45; 6,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 16,16</t>
+          <t>9,5; 16,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 26,86</t>
+          <t>-0,31; 28,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 28,38</t>
+          <t>-1,28; 29,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,51; 59,97</t>
+          <t>24,12; 59,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 15,22</t>
+          <t>-1,36; 15,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 13,66</t>
+          <t>-4,47; 13,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 33,65</t>
+          <t>15,89; 33,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 17,16</t>
+          <t>2,74; 17,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 15,05</t>
+          <t>-1,1; 15,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,47; 40,65</t>
+          <t>22,01; 40,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,24</t>
+          <t>0,41; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,03</t>
+          <t>1,42; 5,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 41,59</t>
+          <t>9,19; 43,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,56</t>
+          <t>0,71; 5,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,33</t>
+          <t>1,52; 6,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,27</t>
+          <t>1,06; 10,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,13</t>
+          <t>0,87; 4,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,07</t>
+          <t>2,12; 5,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 28,91</t>
+          <t>7,8; 25,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 54,1</t>
+          <t>4,18; 56,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 66,68</t>
+          <t>14,44; 70,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100,93; 507,01</t>
+          <t>105,56; 530,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 44,51</t>
+          <t>4,9; 44,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 51,04</t>
+          <t>10,27; 50,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 80,08</t>
+          <t>8,98; 82,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 40,32</t>
+          <t>7,32; 38,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 49,64</t>
+          <t>17,58; 51,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,02; 279,09</t>
+          <t>68,28; 249,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 5,63</t>
+          <t>-1,74; 5,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 4,7</t>
+          <t>-2,55; 4,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,47</t>
+          <t>1,34; 8,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 1,28</t>
+          <t>-6,87; 1,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 4,94</t>
+          <t>-4,35; 4,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,08</t>
+          <t>-0,64; 6,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,52</t>
+          <t>-3,01; 2,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,78</t>
+          <t>-2,54; 3,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,86</t>
+          <t>1,7; 6,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 99,36</t>
+          <t>-21,25; 104,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 74,57</t>
+          <t>-27,18; 71,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,22; 142,49</t>
+          <t>13,97; 145,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 12,49</t>
+          <t>-48,12; 14,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 49,0</t>
+          <t>-29,86; 43,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 70,16</t>
+          <t>-4,26; 70,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 28,81</t>
+          <t>-27,78; 30,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 45,85</t>
+          <t>-22,05; 35,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,78; 82,93</t>
+          <t>15,03; 82,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,07</t>
+          <t>0,32; 4,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,85</t>
+          <t>-0,83; 2,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 29,17</t>
+          <t>5,16; 27,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,06</t>
+          <t>-0,21; 4,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,9</t>
+          <t>-3,38; 1,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 3,53</t>
+          <t>-4,22; 3,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,4</t>
+          <t>0,64; 3,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,39</t>
+          <t>-1,44; 1,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 14,29</t>
+          <t>2,65; 14,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 27,21</t>
+          <t>1,82; 27,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 18,91</t>
+          <t>-5,01; 18,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,15; 184,94</t>
+          <t>31,66; 168,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 15,62</t>
+          <t>-0,76; 15,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 3,52</t>
+          <t>-11,94; 4,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 13,34</t>
+          <t>-14,86; 13,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 16,26</t>
+          <t>2,89; 16,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 6,71</t>
+          <t>-6,59; 6,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 68,41</t>
+          <t>12,08; 65,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,06</t>
+          <t>10,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>11,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,7</t>
+          <t>0,14; 8,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 8,77</t>
+          <t>-0,15; 8,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 17,91</t>
+          <t>5,58; 15,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,29</t>
+          <t>-0,34; 7,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 6,58</t>
+          <t>-2,57; 6,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 15,68</t>
+          <t>7,2; 15,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,07</t>
+          <t>1,11; 6,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 6,05</t>
+          <t>-0,27; 6,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 16,19</t>
+          <t>8,25; 14,25</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 28,54</t>
+          <t>0,44; 28,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 29,82</t>
+          <t>-0,53; 29,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,12; 59,96</t>
+          <t>16,49; 50,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 15,56</t>
+          <t>-0,68; 15,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 13,91</t>
+          <t>-5,12; 13,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 33,61</t>
+          <t>14,37; 32,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 17,68</t>
+          <t>2,7; 17,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 15,08</t>
+          <t>-0,66; 14,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,01; 40,46</t>
+          <t>19,52; 35,64</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,55</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,09</t>
+          <t>10,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,93</t>
+          <t>9,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,21</t>
+          <t>0,2; 4,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,33</t>
+          <t>1,31; 5,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,19; 43,5</t>
+          <t>7,62; 11,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,55</t>
+          <t>0,56; 5,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,2</t>
+          <t>1,49; 6,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,46</t>
+          <t>7,82; 12,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,09</t>
+          <t>0,77; 4,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,18</t>
+          <t>1,97; 5,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 25,58</t>
+          <t>8,31; 11,5</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215,06%</t>
+          <t>112,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>117,46%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 56,49</t>
+          <t>2,01; 53,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 70,81</t>
+          <t>13,57; 67,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105,56; 530,89</t>
+          <t>76,56; 153,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 44,1</t>
+          <t>3,76; 45,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 50,44</t>
+          <t>10,03; 52,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 82,15</t>
+          <t>52,49; 100,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 38,93</t>
+          <t>6,5; 40,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 51,48</t>
+          <t>16,73; 49,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,28; 249,25</t>
+          <t>70,37; 113,74</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>5,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 5,95</t>
+          <t>-1,64; 5,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,42</t>
+          <t>-2,64; 4,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,78</t>
+          <t>1,93; 8,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,48</t>
+          <t>-6,91; 1,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 4,43</t>
+          <t>-3,88; 4,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,84</t>
+          <t>0,55; 7,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,54</t>
+          <t>-2,91; 2,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,13</t>
+          <t>-2,0; 3,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,97</t>
+          <t>2,34; 7,53</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 104,41</t>
+          <t>-19,51; 92,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 71,44</t>
+          <t>-30,5; 78,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,97; 145,68</t>
+          <t>19,76; 141,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 14,5</t>
+          <t>-49,38; 12,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 43,76</t>
+          <t>-27,1; 46,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 70,12</t>
+          <t>3,58; 79,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 30,4</t>
+          <t>-27,05; 33,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 35,97</t>
+          <t>-18,6; 38,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,03; 82,95</t>
+          <t>19,33; 89,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,32</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>4,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,06</t>
+          <t>0,1; 3,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,7</t>
+          <t>-0,74; 2,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 27,04</t>
+          <t>3,54; 7,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,17</t>
+          <t>-0,24; 4,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,14</t>
+          <t>-3,29; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,65</t>
+          <t>1,14; 5,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,43</t>
+          <t>0,59; 3,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,33</t>
+          <t>-1,46; 1,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 14,15</t>
+          <t>2,77; 5,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 27,0</t>
+          <t>0,49; 25,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 18,2</t>
+          <t>-4,38; 17,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,66; 168,82</t>
+          <t>21,03; 49,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 15,92</t>
+          <t>-0,84; 16,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 4,5</t>
+          <t>-11,53; 4,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 13,6</t>
+          <t>3,87; 18,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 16,43</t>
+          <t>2,64; 16,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 6,31</t>
+          <t>-6,58; 6,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,08; 65,0</t>
+          <t>12,6; 26,6</t>
         </is>
       </c>
     </row>
